--- a/十字测试.xlsx
+++ b/十字测试.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAE5AB1-E050-4CB2-B5D1-7DFC3C94F534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67BEABC8-33F5-4046-90A8-DCD79C8C5CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="4" activeTab="19" xr2:uid="{174EABC5-BD9A-4C13-8056-8F53968DDC26}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="4" activeTab="9" xr2:uid="{174EABC5-BD9A-4C13-8056-8F53968DDC26}"/>
   </bookViews>
   <sheets>
     <sheet name="公式" sheetId="19" r:id="rId1"/>
@@ -21,19 +21,18 @@
     <sheet name="Y2" sheetId="31" r:id="rId6"/>
     <sheet name="K" sheetId="1" r:id="rId7"/>
     <sheet name="K^-1" sheetId="9" r:id="rId8"/>
-    <sheet name="e|H=K^T=F^-1" sheetId="5" r:id="rId9"/>
-    <sheet name="S=FK" sheetId="26" r:id="rId10"/>
-    <sheet name="F" sheetId="4" r:id="rId11"/>
-    <sheet name="C" sheetId="6" r:id="rId12"/>
-    <sheet name="gcd(f,g)" sheetId="7" r:id="rId13"/>
-    <sheet name="P (4)" sheetId="23" r:id="rId14"/>
-    <sheet name="P (2)" sheetId="21" r:id="rId15"/>
-    <sheet name="P (3)" sheetId="22" r:id="rId16"/>
-    <sheet name="P" sheetId="20" r:id="rId17"/>
-    <sheet name="gcd(f,p)=g" sheetId="16" r:id="rId18"/>
-    <sheet name="Q" sheetId="12" r:id="rId19"/>
-    <sheet name="X" sheetId="32" r:id="rId20"/>
-    <sheet name="11，14矩阵" sheetId="2" r:id="rId21"/>
+    <sheet name="K^T" sheetId="5" r:id="rId9"/>
+    <sheet name="F" sheetId="4" r:id="rId10"/>
+    <sheet name="C" sheetId="6" r:id="rId11"/>
+    <sheet name="gcd(f,g)" sheetId="7" r:id="rId12"/>
+    <sheet name="P (4)" sheetId="23" r:id="rId13"/>
+    <sheet name="P (2)" sheetId="21" r:id="rId14"/>
+    <sheet name="P (3)" sheetId="22" r:id="rId15"/>
+    <sheet name="P" sheetId="20" r:id="rId16"/>
+    <sheet name="gcd(f,p)=g" sheetId="16" r:id="rId17"/>
+    <sheet name="Q" sheetId="12" r:id="rId18"/>
+    <sheet name="X" sheetId="32" r:id="rId19"/>
+    <sheet name="11，14矩阵" sheetId="2" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>Y</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -343,14 +342,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <fill>
         <patternFill>
@@ -1100,12 +1092,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:C2 C3:C8 B7:B8 B9:C10 C11:C12">
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C14 C15 B16:C17 C18:C19 B20:C24">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1114,4155 +1106,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B774C904-9069-43EB-A027-5F58005940E8}">
-  <dimension ref="A1:AG33"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5">
-        <v>0</v>
-      </c>
-      <c r="W2" s="5">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B3" s="5">
-        <f>MOD(A2+B1+C2,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <f t="shared" ref="C3:AG3" si="0">MOD(B2+C1+D2,2)</f>
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG3" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B4" s="5">
-        <f t="shared" ref="B4:AG4" si="1">MOD(A3+B2+C3,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B5" s="5">
-        <f t="shared" ref="B5:AG5" si="2">MOD(A4+B3+C4,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B6" s="5">
-        <f t="shared" ref="B6:AG6" si="3">MOD(A5+B4+C5,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG6" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B7" s="5">
-        <f t="shared" ref="B7:AG7" si="4">MOD(A6+B5+C6,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AE7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AF7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AG7" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B8" s="5">
-        <f t="shared" ref="B8:AG8" si="5">MOD(A7+B6+C7,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AB8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AC8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AG8" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B9" s="5">
-        <f t="shared" ref="B9:AG9" si="6">MOD(A8+B7+C8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="J9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AC9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AE9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AF9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AG9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B10" s="5">
-        <f t="shared" ref="B10:AG10" si="7">MOD(A9+B8+C9,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="K10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AB10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B11" s="5">
-        <f t="shared" ref="B11:AG11" si="8">MOD(A10+B9+C10,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="L11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B12" s="5">
-        <f t="shared" ref="B12:AG12" si="9">MOD(A11+B10+C11,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="M12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AC12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AE12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AF12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AG12" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B13" s="5">
-        <f t="shared" ref="B13:AG13" si="10">MOD(A12+B11+C12,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="5">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="N13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AC13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AG13" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B14" s="5">
-        <f t="shared" ref="B14:AG14" si="11">MOD(A13+B12+C13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="5">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="O14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AE14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AF14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AG14" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B15" s="5">
-        <f t="shared" ref="B15:AG15" si="12">MOD(A14+B13+C14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="5">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="P15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AG15" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B16" s="5">
-        <f t="shared" ref="B16:AG16" si="13">MOD(A15+B14+C15,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="5">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AF16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AG16" s="5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B17" s="5">
-        <f t="shared" ref="B17:AG17" si="14">MOD(A16+B15+C16,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="R17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AF17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B18" s="5">
-        <f t="shared" ref="B18:AG18" si="15">MOD(A17+B16+C17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="D18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="5">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="S18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AC18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AE18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B19" s="5">
-        <f t="shared" ref="B19:AG19" si="16">MOD(A18+B17+C18,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="E19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="5">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AB19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AC19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AF19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG19" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B20" s="5">
-        <f t="shared" ref="B20:AG20" si="17">MOD(A19+B18+C19,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="D20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="5">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="U20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AC20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AE20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AF20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AG20" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B21" s="5">
-        <f t="shared" ref="B21:AG21" si="18">MOD(A20+B19+C20,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="D21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="R21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="V21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AF21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AG21" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B22" s="5">
-        <f t="shared" ref="B22:AG22" si="19">MOD(A21+B20+C21,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="E22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="5">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="W22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AC22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B23" s="5">
-        <f t="shared" ref="B23:AG23" si="20">MOD(A22+B21+C22,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="5">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="X23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AC23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AG23" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B24" s="5">
-        <f t="shared" ref="B24:AG24" si="21">MOD(A23+B22+C23,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="5">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Y24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AC24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B25" s="5">
-        <f t="shared" ref="B25:AG25" si="22">MOD(A24+B23+C24,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="D25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="5">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="Z25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AC25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B26" s="5">
-        <f t="shared" ref="B26:AG26" si="23">MOD(A25+B24+C25,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="D26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="5">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="AA26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AB26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AE26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AF26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B27" s="5">
-        <f t="shared" ref="B27:AG27" si="24">MOD(A26+B25+C26,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="D27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="5">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="AB27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AC27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AE27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AF27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AG27" s="5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B28" s="5">
-        <f t="shared" ref="B28:AG28" si="25">MOD(A27+B26+C27,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="D28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="E28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AB28" s="5">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="AC28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B29" s="5">
-        <f t="shared" ref="B29:AG29" si="26">MOD(A28+B27+C28,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="D29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="R29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="W29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="X29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="Z29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AB29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AC29" s="5">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AD29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AE29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AG29" s="5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B30" s="5">
-        <f t="shared" ref="B30:AG30" si="27">MOD(A29+B28+C29,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="D30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="R30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AA30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AB30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AC30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="5">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="AE30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AF30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B31" s="5">
-        <f t="shared" ref="B31:AG31" si="28">MOD(A30+B29+C30,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="D31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="R31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="V31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AA31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AB31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AC31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="5">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="AF31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B32" s="5">
-        <f t="shared" ref="B32:AG32" si="29">MOD(A31+B30+C31,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="D32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="N32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="O32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="R32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Z32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AA32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AB32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AC32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AE32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AF32" s="5">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="AG32" s="5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B33" s="5">
-        <f t="shared" ref="B33:AG33" si="30">MOD(A32+B31+C32,2)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="D33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="N33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="O33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="P33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="R33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AA33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AB33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AC33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AD33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AE33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AF33" s="5">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="5">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B2:AG33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437952FC-502A-4F72-8137-18765982E268}">
   <dimension ref="A1:AG33"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -9411,7 +5254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E8B789-2456-4A3D-8DF6-1FA45AFFE964}">
   <dimension ref="A1:AG33"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -13563,7 +9406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBE85A8-39A2-4D00-A9BE-01927FFC7B3F}">
   <dimension ref="A1:BN66"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -20253,7 +16096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7697CBF8-E9A6-4F96-A517-A1C6D79EFA3C}">
   <dimension ref="C3:AG35"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -24368,7 +20211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C471D1B-23AB-4F0D-9735-3605B95736FF}">
   <dimension ref="C3:AG35"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -28483,7 +24326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF8209B2-CBE5-4107-BEBB-24B8E105724A}">
   <dimension ref="C3:AG34"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -32534,7 +28377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0E64E7-3411-414B-9570-15DAC0EAC6BE}">
   <dimension ref="B2:W22"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -34278,7 +30121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D8083B-A503-4097-BED2-925A34804781}">
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -35162,7 +31005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCD3932-4C30-42FF-8336-8BCB51EA6EC7}">
   <dimension ref="B3:U22"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -35844,6 +31687,695 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:A22 V2:XFD22 B3:U22 A23:XFD1048576">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C9F188-3168-4A98-822E-941659AFAAF0}">
+  <dimension ref="B3:U22"/>
+  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="2.5" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B18" s="5">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5">
+        <v>1</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1</v>
+      </c>
+      <c r="M20" s="5">
+        <v>1</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5">
+        <v>1</v>
+      </c>
+      <c r="S20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5">
+        <v>1</v>
+      </c>
+      <c r="M22" s="5">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5">
+        <v>1</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>1</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:XFD1 A2:A22 V2:XFD22 B3:U22 A23:XFD1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39995,7 +36527,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40004,695 +36536,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C9F188-3168-4A98-822E-941659AFAAF0}">
-  <dimension ref="B3:U22"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="5">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5">
-        <v>1</v>
-      </c>
-      <c r="L14" s="5">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5">
-        <v>1</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
-        <v>1</v>
-      </c>
-      <c r="L15" s="5">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5">
-        <v>1</v>
-      </c>
-      <c r="N15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="5">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <v>1</v>
-      </c>
-      <c r="K16" s="5">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>1</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <v>1</v>
-      </c>
-      <c r="K17" s="5">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5">
-        <v>1</v>
-      </c>
-      <c r="N17" s="5">
-        <v>1</v>
-      </c>
-      <c r="O17" s="5">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B18" s="5">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5">
-        <v>1</v>
-      </c>
-      <c r="O19" s="5">
-        <v>1</v>
-      </c>
-      <c r="P19" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B20" s="5">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5">
-        <v>1</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5">
-        <v>1</v>
-      </c>
-      <c r="M20" s="5">
-        <v>1</v>
-      </c>
-      <c r="N20" s="5">
-        <v>1</v>
-      </c>
-      <c r="O20" s="5">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5">
-        <v>1</v>
-      </c>
-      <c r="S20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B21" s="5">
-        <v>0</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5">
-        <v>0</v>
-      </c>
-      <c r="P21" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>0</v>
-      </c>
-      <c r="R21" s="5">
-        <v>0</v>
-      </c>
-      <c r="S21" s="5">
-        <v>0</v>
-      </c>
-      <c r="T21" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5">
-        <v>1</v>
-      </c>
-      <c r="K22" s="5">
-        <v>1</v>
-      </c>
-      <c r="L22" s="5">
-        <v>1</v>
-      </c>
-      <c r="M22" s="5">
-        <v>1</v>
-      </c>
-      <c r="N22" s="5">
-        <v>1</v>
-      </c>
-      <c r="O22" s="5">
-        <v>1</v>
-      </c>
-      <c r="P22" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5">
-        <v>1</v>
-      </c>
-      <c r="T22" s="5">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD1 A2:A22 V2:XFD22 B3:U22 A23:XFD1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6127F479-8B30-4AA5-B055-C31538DBA34E}">
   <dimension ref="B1:BL89"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -52995,32 +48838,32 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD2 X3:XFD3 W3:W8 B3:B22 X4:AY8 AS4:AX9 AZ4:BG10 BH4:BP11 BQ4:XFD12 W9:AY9 AR10:AY10 W10:AL13 AR11:BG11 BG12:BP12 BG13:XFD13 BP14:XFD15 W14:Z16 BG14:BG19 AY15:BF15 AM15:AX19 AA16:AG16 AH16:AL18 AY16:AY19 AZ16:BF21 BP16:BP22 BQ16:XFD24 W17:AG18 W19:AL19 B23:BP24 A25:XFD1048576">
-    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:R18 T18:V19 C19:S19 C20:BG22">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:V17">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA14:AL15">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM14:BF14">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH14:BO22">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54684,17 +50527,17 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z14:AA14">
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG14:BN14">
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56358,17 +52201,17 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:A23 V2:XFD23 B3:U23 A24:XFD1048576">
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z14:AA14">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG14:BN14">
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58032,17 +53875,17 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:A23 V2:XFD23 B3:U23 A24:XFD1048576">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z14:AA14">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG14:BN14">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62187,7 +58030,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:AG33">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -66334,12 +62177,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:AH1 A34:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:XFD14 AH2:AH21 A2:AG33 AK15:AO15 AQ15:XFD15 AK16:XFD21 AH22:XFD33">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70486,7 +66329,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:BH33">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
